--- a/Result/checksun_type/娛樂服務業.xlsx
+++ b/Result/checksun_type/娛樂服務業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>60.73999999999999</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>60.61</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>63.1</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>63.1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>1093663.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>1637307.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>1637307.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>2471726.7</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>4259885.32</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>4259885.32</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-646284.0891911886</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>1093663</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>1093663.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>60.54</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>63.19</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>63.19</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>1080736.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>1903249.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>1903249.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>2950736.2</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>4366673.5</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>4366673.5</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-606101.0226790989</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>1080736</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1080736.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>60.31999999999999</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>60.55</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>63.3</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>60.55</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>63.3</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>3038195.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>2764257.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>2764257.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>3121453.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>4393381.4</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>4393381.4</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-525665.1411375743</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>3038195</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>3038195.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>60.2</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>60.59</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>63.4</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>60.59</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>63.4</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>2082723.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>2562559.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>2562559.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>3556980.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>4430214.38</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>4430214.38</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-601710.7338947686</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>2082723</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>2082723.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>60.3</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>60.73</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>63.52</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>63.52</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>891220.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>2978861.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>2978861</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>3597201.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>4441139.46</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>4441139.46</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-586485.6259088041</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>891220</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>891220.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>60.52</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>60.88</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>63.64</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>63.64</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>2423373.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>3306146.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>3306146</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>3757652.1</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>4461420.58</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>4461420.58</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-416128.5207178257</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>2423373</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2423373.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>60.82000000000001</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>61.04</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>63.76</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>61.04</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>63.76</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>5385778.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>3998223.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>3998223</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>4088204.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>4514488.18</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>4514488.18</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-322058.7447050773</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>5385778</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>5385778.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>60.88</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>61.24</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>63.88</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>63.88</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>2029702.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>3478649.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>3478649.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>3902243.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>4514234.62</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>4514234.62</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-493571.7880902556</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>2029702</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>2029702.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>60.82000000000001</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>61.44</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>63.99</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>61.44</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>63.99</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>4164232.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>4551402.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>4551402.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>4246464.0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>4582184.24</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>4582184.24</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-361383.2862087153</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>4164232</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>4164232.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>60.88</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>61.62</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>64.09</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>61.62</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>64.09</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>2527645.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>4215542.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>4215542</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>4202275.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>4648126.12</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>4648126.12</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-388335.6661562035</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>2527645</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>2527645.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>60.73999999999999</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>61.78</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>64.18</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>61.78</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>64.18000000000001</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>5883758.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>4209158.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>4209158.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>4381203.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>4678124.2</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>4678124.2</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-237621.3280041795</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>5883758</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>5883758.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>157.3</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>159.7</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>160.14</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>159.7</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>160.14</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>15070518.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>15404167.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>15404167</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>23425831.1</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>26442028.38</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>26442028.38</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-3304034.745728541</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>15070518</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>15070518.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>157.1</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>159.88</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>160.24</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>159.88</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>160.24</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>8716040.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>20970134.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>20970134.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>23884396.2</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>26970481.54</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>26970481.54</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-3158033.503715947</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>8716040</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>8716040.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>156.4</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>160.07</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>160.49</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>160.07</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>160.49</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>6311094.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>26752165.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>26752165</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>25227238.4</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>27301703.66</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>27301703.66</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-2155836.461422388</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>6311094</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>6311094.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>155.0</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>160.3</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>160.68</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>160.3</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>160.68</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>22667591.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>32399779.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>32399779.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>30288554.6</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>27943420.14</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>27943420.14</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-389459.4559522159</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>22667591</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>22667591.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>154.5</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>160.5</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>160.81</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>160.81</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>24255592.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>32108499.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>32108499.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>36343945.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>28062881.02</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>28062881.02</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>395363.7110034637</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>24255592</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>24255592.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>154.1</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>160.9</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>160.85</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>160.85</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>42900355.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>31447495.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>31447495.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>38884198.2</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>27918008.04</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>27918008.04</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>1332276.566975739</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>42900355</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>42900355.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>154.4</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>161.25</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>160.92</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>161.25</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>160.92</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>37626193.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>26798658.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>26798658</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>36471220.7</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>27616850.38</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>27616850.38</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>625489.0195441432</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>37626193</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>37626193.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>155.8</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>161.78</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>161.12</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>161.78</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>161.12</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>34549166.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>23702311.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>23702311.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>37857360.7</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>27474428.34</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>27474428.34</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>158542.4153724313</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>34549166</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>34549166.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>157.9</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>162.35</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>161.33</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>162.35</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>161.33</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>21211190.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>28177329.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>28177329.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>35900828.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>27963161.46</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>27963161.46</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-184504.9268504605</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>21211190</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>21211190.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>159.5</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>162.72</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>161.53</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>162.72</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>161.53</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>20950572.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>40579392.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>40579392.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>35598695.6</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>28571680.7</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>28571680.7</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>761085.7602186427</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>20950572</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>20950572.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>162.1</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>163.12</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>161.8</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>163.12</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>161.8</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>19656169.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>46320901.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>46320901.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>36498514.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>30898820.12</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>30898820.12</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>2112671.321738124</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>19656169</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>19656169.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>3.964</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>3.97</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>4.25</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>310.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>186.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>186.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>170.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>216.44</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>216.44</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-5.085874997989606</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>310</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>310.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>3.896</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>3.96</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>4.26</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>4.26</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>18.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>135.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>135.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>147.1</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>211.18</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>211.18</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-21.42116545671452</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>18</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>3.882</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>3.96</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>4.28</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>61.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>135.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>135.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>150.8</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>211.94</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>211.94</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-12.70653877429601</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>61</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>3.904</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>3.96</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>4.3</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>280.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>165.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>165.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>149.8</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>211.48</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>211.48</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-4.410409986044669</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>280</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>280.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>3.922</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>3.97</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>4.32</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>4.32</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>264.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>125.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>125.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>137.9</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>206.14</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>206.14</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-15.8655685033269</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>264</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>264.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>3.928</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>3.98</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>4.34</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>4.34</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>56.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>154.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>154.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>125.8</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>201.02</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>201.02</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-29.94916751003986</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>56</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>3.954</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>3.98</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>4.36</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>4.36</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>17.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>158.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>158.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>132.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>201.1</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>201.1</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-26.71326725141407</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>17</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>3.984</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>4.38</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>211.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>166.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>166</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>136.9</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>201.6</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>201.6</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-16.95793590868388</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>211</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>211.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>3.974</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>4.01</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>4.4</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>81.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>134</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>138.7</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>208.06</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>208.06</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-23.20182199375921</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>81</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>3.972</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>4.03</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>4.42</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>406.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>150</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>143.5</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>212.64</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>212.64</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-17.36445132980396</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>406</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>406.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>3.990000000000001</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>4.05</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>4.44</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>4.44</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>77.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>97.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>97.40000000000001</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>119.5</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>214.04</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>214.04</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-43.22661997666057</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>77</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>91.6</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>92.84</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>90.54</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>92.84</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>90.54000000000001</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>34018.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>23269.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>23269.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>25375.1</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>20196.08</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>20196.08</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>1302.273244028765</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>34018</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>34018.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>92.14</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>93.08</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>90.52</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>93.08</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>90.52</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>27194.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>20304.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>20304.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>23617.0</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>19939.46</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>19939.46</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>466.0883970251343</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>27194</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>27194.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>92.4</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>93.21</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>90.52</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>93.20999999999999</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>90.52</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>14096.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>21669.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>21669.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>22575.3</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>19566.56</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>19566.56</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-13.96454144522795</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>14096</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>14096.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>93.32</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>93.34</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>90.49</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>90.48999999999999</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>13827.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>29288.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>29288.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>22115.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>19553.94</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>19553.94</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>704.1014229344364</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>13827</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>13827.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>93.5</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>93.33</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>90.44</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>90.44</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>27211.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>29946.8</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>29946.8</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>22395.8</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>19406.42</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>19406.42</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>1733.584892657724</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>27211</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>27211.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>93.05999999999999</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>93.46</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>90.35</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>90.34999999999999</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>19195.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>27481.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>27481</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>20789.9</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>19031.22</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>19031.22</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>1708.361817524648</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>19195</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>19195.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>93.61999999999999</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>93.53</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>90.33</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>93.53</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>90.33</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>34019.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>26929.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>26929.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>19751.6</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>18957.08</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>18957.08</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>2470.173073851518</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>34019</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>34019.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>94.25999999999999</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>93.36</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>90.29</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>93.36</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>90.29000000000001</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>52192.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>23481.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>23481</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>17978.6</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>18406.26</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>18406.26</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>1881.968687395205</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>52192</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>52192.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>93.9</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>92.75</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>90.13</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>90.13</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>17117.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>14942.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>14942.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>14564.6</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>17526.18</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>17526.18</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-972.6436035207844</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>17117</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>17117.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>93.94</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>92.31</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>90.04</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>90.04000000000001</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>14882.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>14844.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>14844.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>14755.4</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>17368.58</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>17368.58</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-1257.888176132168</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>14882</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>14882.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>94.05999999999999</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>91.9</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>89.97</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>89.97</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>16437.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>14098.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>14098.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>14361.0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>17251.7</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>17251.7</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-1380.991559286567</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>16437</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>16437.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>16.51</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>16.75</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>16.91</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>16.91</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>1160002.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>12710179.4</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>12710179.4</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>7126454.5</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>2890733.3</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>2890733.3</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>474355.357183394</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>1160002</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>1160002.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>16.51</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>16.76</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>16.91</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>16.91</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>1798814.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>12806386.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>12806386.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>7184891.7</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>2923831.86</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>2923831.86</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>1086071.372957359</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>1798814</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>1798814.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>16.56</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>16.78</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>16.93</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>1905600.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>12876167.8</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>12876167.8</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>7096261.4</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>2926177.76</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>2926177.76</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>1852718.989314548</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>1905600</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>1905600.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>16.65</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>16.81</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>16.95</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>16.95</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>6329974.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>12673438.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>12673438</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>6969080.8</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>2917871.2</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>2917871.2</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>2870319.977349297</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>6329974</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>6329974.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>16.74</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>16.83</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>16.97</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>16.97</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>52356507.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>11800931.8</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>11800931.8</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>6463173.5</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>2841427.64</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>2841427.64</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>3747484.175350748</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>52356507</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>52356507.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>16.78</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>16.84</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>16.98</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>1641039.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>1542729.6</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>1542729.6</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>1423201.1</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>1823439.78</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>1823439.78</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-64677.08376684715</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>1641039</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>1641039.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>16.82</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>16.86</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>16.99</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>16.99</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>2147719.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>1563396.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>1563396.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>1847651.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>1822351.84</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>1822351.84</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-74511.70094316616</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>2147719</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>2147719.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>16.84</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>16.87</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>17</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>891951.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>1316355.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>1316355</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>1781544.4</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>1808610.92</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>1808610.92</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-140187.1647327945</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>891951</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>891951.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>16.86</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>16.88</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>17.01</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>17.01</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>1967443.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>1264723.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>1264723.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>1840160.4</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>1831865.64</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>1831865.64</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-94455.9999775209</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>1967443</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>1967443.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>16.89</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>16.88</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>17.02</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>17.02</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>1065496.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>1125415.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>1125415.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>1784795.4</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>1825444.46</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>1825444.46</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-140983.6217565043</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>1065496</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>1065496.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>16.89</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>16.87</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>17.04</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>1744374.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>1303672.6</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>1303672.6</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>1833097.8</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>1832174.98</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>1832174.98</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-105779.3449494627</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>1744374</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>1744374.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>11.16</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>11.09</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>11.11</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>1912596.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>941047.0</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>941047</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>1678867.9</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>1043889.3</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>1043889.3</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-40485.68657193985</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>1912596</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>1912596.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>11.14</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>11.09</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>11.11</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>189024.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>647763.8</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>647763.8</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>1535017.8</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>1022951.26</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>1022951.26</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-112862.4566016353</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>189024</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>189024.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>11.13</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>11.09</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>11.11</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>575682.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1469771.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1469771.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>1608349.7</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>1032179.18</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>1032179.18</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-27558.61176542751</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>575682</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>575682.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>11.12</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>11.09</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>11.11</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>1685839.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>1617032.6</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>1617032.6</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>1632730.8</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>1028116.62</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>1028116.62</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>53860.61699220608</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>1685839</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>1685839.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>11.13</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>11.09</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>11.11</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>342094.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>1901593.8</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>1901593.8</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>1696488.7</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>1026645.16</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>1026645.16</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>49304.81461053202</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>342094</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>342094.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>11.13</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>11.09</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>11.11</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>446180.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>2416688.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>2416688.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>1867436.3</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>1023856.74</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>1023856.74</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>185008.3178291931</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>446180</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>446180.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>11.14</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>11.12</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>11.12</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>4299061.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>2422271.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>2422271.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>1917587.3</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>1029335.12</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>1029335.12</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>361110.9539333805</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>4299061</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>4299061.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>11.12</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>11.12</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>11.12</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>1311989.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>1746928.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>1746928.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>1552324.8</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>958749.26</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>958749.26</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>186980.6500131707</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>1311989</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>1311989.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>11.11</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>11.12</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>11.12</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>3108645.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>1648429.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>1648429</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>1492221.8</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>955736.2</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>955736.2</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>251588.6211981149</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>3108645</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>3108645.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>11.1</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>11.09</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>11.12</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>11.12</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>2917569.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>1491383.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>1491383.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>1250459.9</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>923462.9</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>923462.9</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>142401.5578481026</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>2917569</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>2917569.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>11.08</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>11.09</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>11.13</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>11.13</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>474095.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>1318183.8</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>1318183.8</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>1127781.0</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>875134.2</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>875134.2</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>1806.697424938553</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>474095</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>474095.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>26.99</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>26.2</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>26.72</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>26.72</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>47864797.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>27431611.6</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>27431611.6</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>25043432.4</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>18916745.36</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>18916745.36</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>3152323.371852718</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>47864797</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>47864797.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>26.52</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>26.69</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>26.69</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>13347769.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>20035167.4</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>20035167.4</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>21346164.0</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>20053847.64</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>20053847.64</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>1250734.083832011</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>13347769</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>13347769.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>26.14</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>26.65</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>26.65</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>34008839.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>22926245.8</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>22926245.8</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>21169800.7</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>20185880.8</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>20185880.8</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>2187761.883665573</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>34008839</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>34008839.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>25.92</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>26.62</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>26.62</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>23214041.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>20521361.2</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>20521361.2</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>18436270.7</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>19763569.86</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>19763569.86</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>1234552.601868317</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>23214041</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>23214041.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>25.97</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>26.17</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>26.6</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>26.6</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>18722612.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>23239204.4</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>23239204.4</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>16731346.9</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>19609581.2</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>19609581.2</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>985319.3920912296</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>18722612</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>18722612.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>26.02</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>26.2</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>26.58</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>26.58</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>10882576.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>22655253.2</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>22655253.2</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>15576861.2</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>19600503.76</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>19600503.76</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>1075306.506977845</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>10882576</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>10882576.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>26.15</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>26.26</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>26.58</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>26.58</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>27803161.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>22657160.6</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>22657160.6</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>15805641.0</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>20656791.76</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>20656791.76</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>2005459.581566658</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>27803161</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>27803161.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>26.28</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>26.32</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>26.57</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>26.57</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>21984416.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>19413355.6</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>19413355.6</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>14446790.8</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>20259042.18</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>20259042.18</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>1449706.310209012</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>21984416</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>21984416.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>26.24</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>26.35</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>26.53</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>26.53</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>36803257.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>16351180.2</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>16351180.2</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>14391909.6</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>20116543.76</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>20116543.76</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>1227434.804333478</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>36803257</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>36803257.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>26.05</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>26.34</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>26.48</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>26.48</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>15802856.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>10223489.4</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>10223489.4</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>11839969.1</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>19718001.5</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>19718001.5</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-721665.8399291933</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>15802856</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>15802856.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>25.95</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>26.34</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>26.44</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>26.44</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>10892113.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>8498469.2</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>8498469.199999999</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>11653050.8</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>20686313.26</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>20686313.26</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-1230278.587449824</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>10892113</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>10892113.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>17.69</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>17.44</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>17.45</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>3157155.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>11054258.6</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>11054258.6</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>6623792.6</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>2730137.84</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>2730137.84</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>1212575.924636489</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>3157155</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>3157155.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>17.6</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>17.44</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>17.45</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>3580789.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>10759263.6</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>10759263.6</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>6430991.9</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>2705050.28</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>2705050.28</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>1818141.083001496</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>3580789</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>3580789.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>17.5</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>17.44</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>17.44</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>17.44</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>15073258.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>10752005.0</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>10752005</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>6241902.6</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>2679225.36</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>2679225.36</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>2572911.199130025</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>15073258</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>15073258.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>17.45</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>17.44</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>17.44</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>17.44</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>32434967.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>8124323.0</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>8124323</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>4856369.3</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>2470703.76</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>2470703.76</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>2327928.57220185</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>32434967</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>32434967.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>17.21</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>17.38</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>17.43</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>17.43</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>1025124.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>2090894.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>2090894</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>1796794.1</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>1997944.66</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>1997944.66</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>34629.97758296179</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>1025124</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>1025124.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>17.25</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>17.39</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>17.43</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>17.43</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>1682180.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>2193326.6</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>2193326.6</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>1837028.8</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>2085077.28</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>2085077.28</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>122592.664642303</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>1682180</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>1682180.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>17.3</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>17.4</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>17.43</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>17.43</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>3544496.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>2102720.2</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>2102720.2</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>1781544.9</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>2094464.9</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>2094464.9</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>173476.4795612798</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>3544496</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>3544496.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>17.36</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>17.42</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>17.42</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>17.42</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>1934848.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>1731800.2</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>1731800.2</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>1613463.5</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>2036524.48</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>2036524.48</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>40438.19803262944</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>1934848</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>1934848.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>17.37</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>17.42</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>17.41</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>17.41</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>2267822.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>1588415.6</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>1588415.6</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>1554873.0</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>2016801.22</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>2016801.22</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>21401.57449053484</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>2267822</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>2267822.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>17.38</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>17.42</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>17.4</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>17.4</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>1537287.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>1502694.2</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>1502694.2</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>1507448.6</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>1994126.0</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>1994126</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-42233.72965854802</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>1537287</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>1537287.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>17.4</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>17.42</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>17.39</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>17.39</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>1229148.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>1480731.0</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>1480731</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>1506760.6</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>1984841.4</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>1984841.4</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-53361.35238371813</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>1229148</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>1229148.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
